--- a/回路/買うものリスト.xlsx
+++ b/回路/買うものリスト.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tauchi/github/EasyMeasurementCamera/回路/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtauc\github\EasyMeasurementCamera\回路\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775F3230-8D4D-DD47-8AC6-34BE5C97DAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6A10B9-2B79-4EDC-9209-ACDAE4F1D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="820" windowWidth="28300" windowHeight="17360" xr2:uid="{52CC9F33-00BB-B04F-95CA-B195ADE97EA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{52CC9F33-00BB-B04F-95CA-B195ADE97EA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Ver_1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>品名</t>
     <rPh sb="0" eb="2">
@@ -111,6 +111,37 @@
   </si>
   <si>
     <t>マイコン内蔵LED</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベルコンバータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g118329/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TC7WPB9307FK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WS2813B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤色LED</t>
+    <rPh sb="0" eb="2">
+      <t>アカイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g111879/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SML-E12V8WT86</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -118,7 +149,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -511,18 +542,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7BF6CC-F9E9-364F-B5C2-0C4566E92636}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -545,7 +576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -566,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -586,21 +617,60 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>14</v>
       </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>150</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <v>1608</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="F4" r:id="rId1" xr:uid="{2A3E2AAD-B52E-A146-8E8E-D7A4AD076B9B}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{B397B771-9A51-44E7-9693-11338CB6EF0D}"/>
+    <hyperlink ref="F6" r:id="rId3" xr:uid="{FF2A3DE6-373F-410E-9F8A-203F6264CDF5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/回路/買うものリスト.xlsx
+++ b/回路/買うものリスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtauc\github\EasyMeasurementCamera\回路\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6A10B9-2B79-4EDC-9209-ACDAE4F1D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3906FC7E-5F5F-4038-B585-F952BB9BFBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{52CC9F33-00BB-B04F-95CA-B195ADE97EA1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>品名</t>
     <rPh sb="0" eb="2">
@@ -95,9 +95,6 @@
     <t>https://akizukidenshi.com/catalog/g/g115178/</t>
   </si>
   <si>
-    <t>https://akizukidenshi.com/catalog/g/g102913/</t>
-  </si>
-  <si>
     <t>フォトカプラ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -142,6 +139,25 @@
   </si>
   <si>
     <t>SML-E12V8WT86</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g105318</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NSSW157T</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白色LED</t>
+    <rPh sb="0" eb="2">
+      <t>ハクショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://akizukidenshi.com/catalog/g/g102913/</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -542,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7BF6CC-F9E9-364F-B5C2-0C4566E92636}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
@@ -599,10 +615,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
       </c>
       <c r="C3">
         <v>380</v>
@@ -613,16 +629,16 @@
       <c r="E3">
         <v>380</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -631,15 +647,15 @@
         <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>150</v>
@@ -648,21 +664,32 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="G6">
         <v>1608</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -671,6 +698,8 @@
     <hyperlink ref="F4" r:id="rId1" xr:uid="{2A3E2AAD-B52E-A146-8E8E-D7A4AD076B9B}"/>
     <hyperlink ref="F5" r:id="rId2" xr:uid="{B397B771-9A51-44E7-9693-11338CB6EF0D}"/>
     <hyperlink ref="F6" r:id="rId3" xr:uid="{FF2A3DE6-373F-410E-9F8A-203F6264CDF5}"/>
+    <hyperlink ref="F7" r:id="rId4" xr:uid="{74C9666C-A710-40DB-9F56-74866601B28B}"/>
+    <hyperlink ref="F3" r:id="rId5" xr:uid="{78332463-CCB6-471F-9386-8C972D8607DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
